--- a/成績管理システム_ユースケースから画面遷移書.xlsx
+++ b/成績管理システム_ユースケースから画面遷移書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.22.65.11\602-Students$\谷口\Java応用\2025年度前期課題提出先（金曜３－４限）\23A32F0005_吉田匠太郎\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri34ys\seiseki_manage_sys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{D50530FE-D09D-4ABE-84BC-81E7FEF71B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7793502E-7C5C-4AB9-895F-AB8EDBC63693}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B768742D-816A-4D24-AF19-5B76892FC9B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース図" sheetId="1" r:id="rId1"/>
@@ -29,10 +29,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -158,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5726,8 +5726,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9677400" y="4286250"/>
-          <a:ext cx="1219200" cy="361950"/>
+          <a:off x="10240736" y="5889171"/>
+          <a:ext cx="1213757" cy="368754"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10267,21 +10267,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D6:M57"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="21.75" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:10" ht="25.5">
+    <row r="6" spans="4:10" ht="25.5" x14ac:dyDescent="0.5">
       <c r="J6" s="7"/>
     </row>
-    <row r="16" spans="4:10" ht="33">
+    <row r="16" spans="4:10" ht="33" x14ac:dyDescent="0.65">
       <c r="D16" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="4:13" ht="33">
+    <row r="43" spans="4:13" ht="33" x14ac:dyDescent="0.65">
       <c r="D43" s="6" t="s">
         <v>1</v>
       </c>
@@ -10289,10 +10289,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="4:13" ht="33">
+    <row r="47" spans="4:13" ht="33" x14ac:dyDescent="0.65">
       <c r="D47" s="1"/>
     </row>
-    <row r="57" spans="4:4" ht="33">
+    <row r="57" spans="4:4" ht="33" x14ac:dyDescent="0.65">
       <c r="D57" s="6" t="s">
         <v>3</v>
       </c>
@@ -10307,7 +10307,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A587C7C4-AF37-4D8C-B0C6-57361D8E31A4}">
   <dimension ref="C4:U67"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9" style="11"/>
     <col min="3" max="3" width="36" style="11" bestFit="1" customWidth="1"/>
@@ -10329,11 +10329,11 @@
     <col min="21" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:20">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="6" spans="3:20" ht="15.75">
+    <row r="6" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -10348,7 +10348,7 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="12"/>
     </row>
-    <row r="7" spans="3:20" ht="15.75">
+    <row r="7" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
@@ -10364,7 +10364,7 @@
       <c r="R7" s="14"/>
       <c r="T7" s="14"/>
     </row>
-    <row r="8" spans="3:20" ht="15.75">
+    <row r="8" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="20" t="s">
@@ -10382,7 +10382,7 @@
       <c r="R8" s="14"/>
       <c r="T8" s="14"/>
     </row>
-    <row r="9" spans="3:20" ht="15.75">
+    <row r="9" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
@@ -10398,7 +10398,7 @@
       <c r="R9" s="14"/>
       <c r="T9" s="14"/>
     </row>
-    <row r="10" spans="3:20" ht="15.75">
+    <row r="10" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
@@ -10414,7 +10414,7 @@
       <c r="R10" s="14"/>
       <c r="T10" s="14"/>
     </row>
-    <row r="11" spans="3:20" ht="15.75">
+    <row r="11" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
@@ -10430,7 +10430,7 @@
       <c r="R11" s="14"/>
       <c r="T11" s="14"/>
     </row>
-    <row r="12" spans="3:20" ht="15.75">
+    <row r="12" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
@@ -10446,7 +10446,7 @@
       <c r="R12" s="14"/>
       <c r="T12" s="14"/>
     </row>
-    <row r="13" spans="3:20" ht="15.75">
+    <row r="13" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
@@ -10462,7 +10462,7 @@
       <c r="R13" s="14"/>
       <c r="T13" s="14"/>
     </row>
-    <row r="14" spans="3:20" ht="15.75">
+    <row r="14" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
@@ -10470,11 +10470,11 @@
       <c r="G14" s="15"/>
       <c r="H14" s="14"/>
     </row>
-    <row r="19" spans="3:19" ht="15.75">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C19" s="16"/>
       <c r="M19" s="10"/>
     </row>
-    <row r="21" spans="3:19" ht="15.75">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
@@ -10490,7 +10490,7 @@
       <c r="R21" s="12"/>
       <c r="S21" s="14"/>
     </row>
-    <row r="22" spans="3:19" ht="15.75">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
@@ -10506,7 +10506,7 @@
       <c r="R22" s="14"/>
       <c r="S22" s="14"/>
     </row>
-    <row r="23" spans="3:19" ht="15.75">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
@@ -10522,7 +10522,7 @@
       <c r="R23" s="14"/>
       <c r="S23" s="14"/>
     </row>
-    <row r="24" spans="3:19" ht="15.75">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
@@ -10538,7 +10538,7 @@
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
     </row>
-    <row r="25" spans="3:19" ht="15.75">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.4">
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -10554,7 +10554,7 @@
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
     </row>
-    <row r="26" spans="3:19" ht="15.75">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.4">
       <c r="M26" s="14"/>
       <c r="N26" s="14"/>
       <c r="O26" s="14"/>
@@ -10563,11 +10563,11 @@
       <c r="R26" s="14"/>
       <c r="S26" s="14"/>
     </row>
-    <row r="33" spans="3:20">
+    <row r="33" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C33" s="10"/>
       <c r="M33" s="10"/>
     </row>
-    <row r="35" spans="3:20">
+    <row r="35" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -10585,7 +10585,7 @@
       <c r="S35" s="18"/>
       <c r="T35" s="18"/>
     </row>
-    <row r="36" spans="3:20">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
@@ -10603,7 +10603,7 @@
       <c r="S36" s="18"/>
       <c r="T36" s="18"/>
     </row>
-    <row r="37" spans="3:20">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
@@ -10621,7 +10621,7 @@
       <c r="S37" s="18"/>
       <c r="T37" s="18"/>
     </row>
-    <row r="38" spans="3:20">
+    <row r="38" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
@@ -10639,7 +10639,7 @@
       <c r="S38" s="18"/>
       <c r="T38" s="18"/>
     </row>
-    <row r="39" spans="3:20">
+    <row r="39" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
@@ -10657,7 +10657,7 @@
       <c r="S39" s="18"/>
       <c r="T39" s="18"/>
     </row>
-    <row r="40" spans="3:20" ht="15.75">
+    <row r="40" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
@@ -10675,7 +10675,7 @@
       <c r="S40" s="18"/>
       <c r="T40" s="18"/>
     </row>
-    <row r="41" spans="3:20">
+    <row r="41" spans="3:20" x14ac:dyDescent="0.4">
       <c r="M41" s="18"/>
       <c r="N41" s="18"/>
       <c r="O41" s="18"/>
@@ -10685,7 +10685,7 @@
       <c r="S41" s="18"/>
       <c r="T41" s="18"/>
     </row>
-    <row r="42" spans="3:20" ht="15.75">
+    <row r="42" spans="3:20" x14ac:dyDescent="0.4">
       <c r="M42" s="18"/>
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
@@ -10693,11 +10693,11 @@
       <c r="Q42" s="19"/>
       <c r="R42" s="18"/>
     </row>
-    <row r="47" spans="3:20">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.4">
       <c r="C47" s="10"/>
       <c r="M47" s="10"/>
     </row>
-    <row r="49" spans="3:21">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
@@ -10716,7 +10716,7 @@
       <c r="T49" s="18"/>
       <c r="U49" s="18"/>
     </row>
-    <row r="50" spans="3:21">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
       <c r="E50" s="18"/>
@@ -10735,7 +10735,7 @@
       <c r="T50" s="18"/>
       <c r="U50" s="18"/>
     </row>
-    <row r="51" spans="3:21">
+    <row r="51" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
       <c r="E51" s="18"/>
@@ -10754,7 +10754,7 @@
       <c r="T51" s="18"/>
       <c r="U51" s="18"/>
     </row>
-    <row r="52" spans="3:21">
+    <row r="52" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C52" s="18"/>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
@@ -10773,7 +10773,7 @@
       <c r="T52" s="18"/>
       <c r="U52" s="18"/>
     </row>
-    <row r="53" spans="3:21">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
       <c r="E53" s="18"/>
@@ -10792,7 +10792,7 @@
       <c r="T53" s="18"/>
       <c r="U53" s="18"/>
     </row>
-    <row r="54" spans="3:21">
+    <row r="54" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
       <c r="E54" s="18"/>
@@ -10811,7 +10811,7 @@
       <c r="T54" s="18"/>
       <c r="U54" s="18"/>
     </row>
-    <row r="55" spans="3:21" ht="15.75">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
       <c r="E55" s="18"/>
@@ -10830,7 +10830,7 @@
       <c r="T55" s="18"/>
       <c r="U55" s="18"/>
     </row>
-    <row r="56" spans="3:21" ht="15.75">
+    <row r="56" spans="3:21" x14ac:dyDescent="0.4">
       <c r="M56" s="18"/>
       <c r="N56" s="18"/>
       <c r="O56" s="18"/>
@@ -10841,7 +10841,7 @@
       <c r="T56" s="18"/>
       <c r="U56" s="18"/>
     </row>
-    <row r="57" spans="3:21" ht="15.75">
+    <row r="57" spans="3:21" x14ac:dyDescent="0.4">
       <c r="M57" s="18"/>
       <c r="N57" s="18"/>
       <c r="O57" s="18"/>
@@ -10852,7 +10852,7 @@
       <c r="T57" s="18"/>
       <c r="U57" s="18"/>
     </row>
-    <row r="61" spans="3:21">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
@@ -10860,7 +10860,7 @@
       <c r="G61" s="17"/>
       <c r="H61" s="17"/>
     </row>
-    <row r="62" spans="3:21">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
       <c r="E62" s="18"/>
@@ -10868,7 +10868,7 @@
       <c r="G62" s="18"/>
       <c r="H62" s="18"/>
     </row>
-    <row r="63" spans="3:21" ht="15.75">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
@@ -10882,7 +10882,7 @@
       <c r="Q63" s="15"/>
       <c r="R63" s="14"/>
     </row>
-    <row r="64" spans="3:21">
+    <row r="64" spans="3:21" x14ac:dyDescent="0.4">
       <c r="C64" s="18"/>
       <c r="D64" s="18"/>
       <c r="E64" s="18"/>
@@ -10890,7 +10890,7 @@
       <c r="G64" s="18"/>
       <c r="H64" s="18"/>
     </row>
-    <row r="65" spans="3:8">
+    <row r="65" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
@@ -10898,7 +10898,7 @@
       <c r="G65" s="18"/>
       <c r="H65" s="18"/>
     </row>
-    <row r="66" spans="3:8">
+    <row r="66" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
@@ -10906,7 +10906,7 @@
       <c r="G66" s="18"/>
       <c r="H66" s="18"/>
     </row>
-    <row r="67" spans="3:8" ht="15.75">
+    <row r="67" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
       <c r="E67" s="18"/>
@@ -10926,7 +10926,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA13E3A-8C7A-44F7-B000-4D19323B9E80}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10938,12 +10938,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3A7CDF-40EE-4E2B-942F-AAE76AE5F7BE}">
   <dimension ref="B2:U54"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="76.5">
+    <row r="2" spans="2:14" ht="76.5" x14ac:dyDescent="1.45">
       <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
@@ -10960,20 +10960,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="76.5">
+    <row r="11" spans="2:14" ht="76.5" x14ac:dyDescent="1.45">
       <c r="B11" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="6:21">
+    <row r="17" spans="6:21" x14ac:dyDescent="0.4">
       <c r="F17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="6:21">
+    <row r="18" spans="6:21" x14ac:dyDescent="0.4">
       <c r="R18" s="5"/>
     </row>
-    <row r="19" spans="6:21">
+    <row r="19" spans="6:21" x14ac:dyDescent="0.4">
       <c r="J19" s="5" t="s">
         <v>7</v>
       </c>
@@ -10984,41 +10984,41 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="6:21">
+    <row r="22" spans="6:21" x14ac:dyDescent="0.4">
       <c r="U22" s="5"/>
     </row>
-    <row r="33" spans="2:19" ht="76.5">
+    <row r="33" spans="2:19" ht="76.5" x14ac:dyDescent="1.45">
       <c r="B33" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="2:19">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.4">
       <c r="F37" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="2:19">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.4">
       <c r="M39" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="2:19">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.4">
       <c r="O41" s="5"/>
       <c r="S41" s="5"/>
     </row>
-    <row r="44" spans="2:19">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.4">
       <c r="M44" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:19">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.4">
       <c r="R47" s="5"/>
     </row>
-    <row r="48" spans="2:19">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.4">
       <c r="O48" s="4"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="54" spans="10:10">
+    <row r="54" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J54" s="8"/>
     </row>
   </sheetData>
@@ -11032,19 +11032,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BFC89EF-2680-456E-BF78-77507EEACBB0}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>18</v>
       </c>

--- a/成績管理システム_ユースケースから画面遷移書.xlsx
+++ b/成績管理システム_ユースケースから画面遷移書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri34ys\seiseki_manage_sys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B768742D-816A-4D24-AF19-5B76892FC9B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C23F96-A352-415B-9558-F1443D487C5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース図" sheetId="1" r:id="rId1"/>
@@ -24,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>各教師</t>
   </si>
@@ -151,6 +140,10 @@
   </si>
   <si>
     <t>DB: MySQL</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>scoresテーブル、class_id追加未</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -10925,9 +10918,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA13E3A-8C7A-44F7-B000-4D19323B9E80}">
-  <dimension ref="A1"/>
+  <dimension ref="M59"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="59" spans="13:13" x14ac:dyDescent="0.4">
+      <c r="M59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/成績管理システム_ユースケースから画面遷移書.xlsx
+++ b/成績管理システム_ユースケースから画面遷移書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri34ys\seiseki_manage_sys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{85C23F96-A352-415B-9558-F1443D487C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E493790-108A-4B86-B829-9FED7F229DE2}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{85C23F96-A352-415B-9558-F1443D487C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA71DD0-E760-4B12-9D5D-86B356AB75FC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" firstSheet="4" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース図" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="86">
+  <si>
+    <t>未実装の部分</t>
+  </si>
   <si>
     <t>各教師</t>
   </si>
@@ -133,22 +136,23 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>言語: Java</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンゴ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
+    <t>プログラミング言語: Java</t>
   </si>
   <si>
-    <t>環境: Eclipse</t>
-    <rPh sb="0" eb="2">
-      <t>カンキョウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
+    <t>フレームワーク: Spring</t>
+  </si>
+  <si>
+    <t>テンプレートエンジン: Thymeleaf</t>
+  </si>
+  <si>
+    <t>開発環境: Eclipse</t>
   </si>
   <si>
     <t>DB: MySQL</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*該当データを使う処理が未実装</t>
   </si>
   <si>
     <t>studentsテーブル</t>
@@ -459,7 +463,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +473,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,7 +571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -596,6 +612,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1206,7 +1233,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69289383-507C-49B8-8808-56E7C4B9DBAD}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{61C9E917-92AD-45DF-B0D7-AF8648B87284}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7CBD1A4F-33C1-FFC9-7719-F5381D6C3783}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1734,7 +1761,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{808CB00D-2149-488C-8F31-D83F15338714}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{ABE58296-B0CE-4B46-996A-DAF4458E5395}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{431A589F-1820-47FE-9E23-30ED08E05657}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2185,7 +2212,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{002A79BA-EB2A-42ED-A340-3ECBD49AC6AE}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{84D80909-9C93-4AB2-A8D1-D75E249C1DDA}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15A56B17-D359-4D66-9495-220B62FEEB95}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2509,7 +2536,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{249CFD04-16BC-4B70-9315-B377A633990B}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{84D80909-9C93-4AB2-A8D1-D75E249C1DDA}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C5B4E316-F495-4DF7-9AB3-C9FAD65DFA02}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2524,9 +2551,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg2"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -2720,9 +2745,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg2"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -3316,7 +3339,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21FC8C3E-219A-4EDC-9B04-5F8BE1001A9F}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{431A589F-1820-47FE-9E23-30ED08E05657}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C151A1AA-9BA8-47D9-8BF5-5FDED2EEB63F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3331,9 +3354,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg2"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -3529,9 +3550,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg2"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -3817,6 +3836,200 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="楕円 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFEC47DE-AF99-447D-ADB9-5DFC323F3CBF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2BED5776-D4E5-4BD1-991B-B0C16CBDC0D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5657850" y="12906375"/>
+          <a:ext cx="2181225" cy="923925"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>管理者情報</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>閲覧</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3824,23 +4037,26 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ACE24E7-847E-2B51-DA65-88F8FF097715}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{341EF3B7-79FE-5AF4-EE46-E59A03542898}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5ACE24E7-847E-2B51-DA65-88F8FF097715}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3850,15 +4066,14 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="17145" t="14400" r="27810" b="30560"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9010650" y="9896475"/>
-          <a:ext cx="2514600" cy="1419225"/>
+          <a:off x="180975" y="2724150"/>
+          <a:ext cx="10391775" cy="5905500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7441,281 +7656,6 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>424541</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>166007</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>367391</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>242207</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="四角形 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9706E8B-2AFD-8D5F-4A05-4A9963AC33C7}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A55AFA91-9032-2EBA-8858-5F765DCAF5C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17392648" y="24128186"/>
-          <a:ext cx="4705350" cy="4239985"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent5">
-              <a:lumMod val="60000"/>
-              <a:lumOff val="40000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>画面遷移 （戻りについて）</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>1.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>入力</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>登録確定したら、詳細へ</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-lt"/>
-            <a:cs typeface="+mn-lt"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>2. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>成績</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1800">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>情報修正したら、詳細へ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -10782,19 +10722,22 @@
   </cols>
   <sheetData>
     <row r="6" spans="4:10" ht="25.5">
+      <c r="D6" s="28" t="s">
+        <v>0</v>
+      </c>
       <c r="J6" s="7"/>
     </row>
     <row r="16" spans="4:10" ht="33">
       <c r="D16" s="6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="4:13" ht="33">
       <c r="D43" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="4:13" ht="33">
@@ -10802,7 +10745,7 @@
     </row>
     <row r="57" spans="4:4" ht="33">
       <c r="D57" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10834,29 +10777,29 @@
   <sheetData>
     <row r="2" spans="2:14" ht="76.5">
       <c r="B2" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="9"/>
       <c r="F2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="J3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="76.5">
       <c r="B11" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="6:21">
       <c r="F17" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="6:21">
@@ -10864,13 +10807,13 @@
     </row>
     <row r="19" spans="6:21">
       <c r="J19" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="6:21">
@@ -10878,17 +10821,17 @@
     </row>
     <row r="33" spans="2:19" ht="76.5">
       <c r="B33" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="2:19">
       <c r="F37" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="2:19">
       <c r="M39" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="2:19">
@@ -10897,7 +10840,7 @@
     </row>
     <row r="44" spans="2:19">
       <c r="M44" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="2:19">
@@ -10920,22 +10863,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BFC89EF-2680-456E-BF78-77507EEACBB0}">
-  <dimension ref="B2:B4"/>
+  <dimension ref="B2:B6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10947,7 +10900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EC819A-7AE1-4C75-BFBB-64D451D6BF2E}">
-  <dimension ref="B2:G140"/>
+  <dimension ref="B1:G140"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9" style="11"/>
@@ -10956,13 +10909,18 @@
     <col min="4" max="4" width="22.75" style="11" customWidth="1"/>
     <col min="5" max="5" width="14.625" style="11" customWidth="1"/>
     <col min="6" max="6" width="17.75" style="11" customWidth="1"/>
-    <col min="7" max="7" width="26.625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="28.125" style="11" customWidth="1"/>
     <col min="8" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:7">
+      <c r="G1" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="2" spans="2:7">
       <c r="B2" s="23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -10980,197 +10938,197 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C6" s="13">
         <v>2</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" s="14">
         <v>3</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8" s="14">
         <v>4</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C9" s="14">
         <v>6</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" s="13">
         <v>7</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G10" s="13"/>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C11" s="14">
         <v>8</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C12" s="14">
         <v>8</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" s="14">
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" s="13">
         <v>9</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G14" s="13"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="23" t="s">
-        <v>49</v>
+      <c r="B25" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -11188,127 +11146,127 @@
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C28" s="13">
         <v>1</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C29" s="14">
         <v>3</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C30" s="14">
         <v>4</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C31" s="14">
         <v>8</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C32" s="14">
         <v>8</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G32" s="14"/>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C33" s="15">
         <v>9</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G33" s="13"/>
     </row>
@@ -11348,265 +11306,265 @@
       <c r="G43"/>
     </row>
     <row r="46" spans="2:7">
-      <c r="B46" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="22"/>
+      <c r="B46" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="26"/>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C49" s="19">
         <v>1</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C50" s="19">
         <v>2</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C51" s="14">
         <v>8</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C52" s="14">
         <v>8</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C53" s="14">
         <v>8</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G53" s="14"/>
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C54" s="15">
         <v>9</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G54" s="13"/>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="21" t="s">
-        <v>59</v>
+      <c r="B56" s="24" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="2:7">
       <c r="B59" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C59" s="19">
         <v>1</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="2:7">
       <c r="B60" s="19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C60" s="19">
         <v>2</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G60" s="19"/>
     </row>
     <row r="61" spans="2:7">
       <c r="B61" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C61" s="14">
         <v>3</v>
       </c>
       <c r="D61" s="14"/>
       <c r="E61" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G61" s="14"/>
     </row>
     <row r="62" spans="2:7">
       <c r="B62" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C62" s="14">
         <v>8</v>
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="2:7">
       <c r="B63" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C63" s="14">
         <v>6</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G63" s="14"/>
     </row>
     <row r="64" spans="2:7">
       <c r="B64" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C64" s="15">
         <v>7</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G64" s="13"/>
     </row>
@@ -11614,951 +11572,943 @@
       <c r="B66" s="18"/>
     </row>
     <row r="68" spans="2:7">
-      <c r="B68" s="21" t="s">
-        <v>64</v>
+      <c r="B68" s="24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="2:7">
       <c r="B71" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C71" s="19">
         <v>1</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="2:7">
       <c r="B72" s="19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C72" s="19">
         <v>2</v>
       </c>
       <c r="D72" s="19"/>
       <c r="E72" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G72" s="19"/>
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C73" s="14">
         <v>3</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G73" s="14"/>
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C74" s="14">
         <v>7</v>
       </c>
       <c r="D74" s="14"/>
       <c r="E74" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="2:7">
       <c r="B75" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C75" s="14">
         <v>7</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G75" s="14"/>
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C76" s="15">
         <v>8</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G76" s="13"/>
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C84" s="19">
         <v>1</v>
       </c>
       <c r="D84" s="19"/>
       <c r="E84" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C85" s="19">
         <v>2</v>
       </c>
       <c r="D85" s="19"/>
       <c r="E85" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G85" s="19"/>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C86" s="14">
         <v>3</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G86" s="14"/>
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C87" s="15">
         <v>4</v>
       </c>
       <c r="D87" s="16"/>
       <c r="E87" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G87" s="13"/>
     </row>
     <row r="88" spans="2:7">
       <c r="B88" s="19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C88" s="19">
         <v>5</v>
       </c>
       <c r="D88" s="19"/>
       <c r="E88" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G88" s="19"/>
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C89" s="14">
         <v>6</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="2:7">
       <c r="B90" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C90" s="14">
         <v>6</v>
       </c>
       <c r="D90" s="14"/>
       <c r="E90" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G90" s="14"/>
     </row>
     <row r="91" spans="2:7">
       <c r="B91" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C91" s="14">
         <v>6</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G91" s="14"/>
     </row>
     <row r="92" spans="2:7">
       <c r="B92" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C92" s="15">
         <v>7</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G92" s="13"/>
     </row>
     <row r="94" spans="2:7">
       <c r="B94" s="21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C94" s="22"/>
     </row>
     <row r="96" spans="2:7">
       <c r="B96" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="2:7">
       <c r="B97" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C97" s="19">
         <v>1</v>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="2:7">
       <c r="B98" s="19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C98" s="19">
         <v>2</v>
       </c>
       <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="2:7">
       <c r="B99" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C99" s="14">
         <v>3</v>
       </c>
       <c r="D99" s="14"/>
       <c r="E99" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="2:7">
       <c r="B100" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C100" s="15">
         <v>4</v>
       </c>
       <c r="D100" s="16"/>
       <c r="E100" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="2:7">
       <c r="B101" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C101" s="14">
         <v>6</v>
       </c>
       <c r="D101" s="14"/>
       <c r="E101" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G101" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102" spans="2:7">
       <c r="B102" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C102" s="14">
         <v>6</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C103" s="14">
         <v>6</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G103" s="14"/>
     </row>
     <row r="104" spans="2:7">
       <c r="B104" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C104" s="15">
         <v>7</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G104" s="13"/>
     </row>
     <row r="106" spans="2:7">
       <c r="B106" s="21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="2:7">
       <c r="B108" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="2:7">
       <c r="B109" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C109" s="19">
         <v>1</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F109" s="19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="2:7">
       <c r="B110" s="19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C110" s="19">
         <v>2</v>
       </c>
       <c r="D110" s="19"/>
       <c r="E110" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F110" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="2:7">
       <c r="B111" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C111" s="14">
         <v>3</v>
       </c>
       <c r="D111" s="14"/>
       <c r="E111" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G111" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="112" spans="2:7">
       <c r="B112" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C112" s="15">
         <v>4</v>
       </c>
       <c r="D112" s="16"/>
       <c r="E112" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F112" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="113" spans="2:7">
       <c r="B113" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C113" s="14">
         <v>6</v>
       </c>
       <c r="D113" s="14"/>
       <c r="E113" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114" spans="2:7">
       <c r="B114" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C114" s="14">
         <v>6</v>
       </c>
       <c r="D114" s="14"/>
       <c r="E114" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115" spans="2:7">
       <c r="B115" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C115" s="14">
         <v>6</v>
       </c>
       <c r="D115" s="14"/>
       <c r="E115" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G115" s="14"/>
     </row>
     <row r="116" spans="2:7">
       <c r="B116" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C116" s="14">
         <v>6</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G116" s="14"/>
     </row>
     <row r="117" spans="2:7">
       <c r="B117" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C117" s="15">
         <v>7</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G117" s="13"/>
     </row>
     <row r="119" spans="2:7">
-      <c r="B119" s="21" t="s">
-        <v>79</v>
+      <c r="B119" s="24" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="2:7">
       <c r="B121" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="2:7">
       <c r="B122" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C122" s="19">
         <v>1</v>
       </c>
       <c r="D122" s="19"/>
       <c r="E122" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F122" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="2:7">
       <c r="B123" s="19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C123" s="19">
         <v>2</v>
       </c>
       <c r="D123" s="19"/>
       <c r="E123" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G123" s="19"/>
     </row>
     <row r="124" spans="2:7">
       <c r="B124" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C124" s="14">
         <v>3</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G124" s="14"/>
     </row>
     <row r="125" spans="2:7">
       <c r="B125" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C125" s="15">
         <v>4</v>
       </c>
       <c r="D125" s="16"/>
       <c r="E125" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F125" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G125" s="13"/>
     </row>
     <row r="126" spans="2:7">
       <c r="B126" s="19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C126" s="19">
         <v>5</v>
       </c>
       <c r="D126" s="19"/>
       <c r="E126" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F126" s="19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G126" s="19"/>
     </row>
     <row r="127" spans="2:7">
       <c r="B127" s="14" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C127" s="14">
         <v>6</v>
       </c>
-      <c r="D127" s="14"/>
+      <c r="D127" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="E127" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F127" s="14" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G127" s="14"/>
     </row>
     <row r="128" spans="2:7">
-      <c r="B128" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C128" s="14">
-        <v>6</v>
-      </c>
-      <c r="D128" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E128" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G128" s="14"/>
+      <c r="B128" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C128" s="15">
+        <v>7</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F128" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G128" s="13"/>
     </row>
     <row r="129" spans="2:7">
-      <c r="B129" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C129" s="15">
-        <v>7</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E129" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="B129" s="13"/>
+      <c r="C129" s="15"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="17"/>
+      <c r="F129" s="13"/>
       <c r="G129" s="13"/>
     </row>
     <row r="132" spans="2:7">
       <c r="B132" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="134" spans="2:7">
       <c r="B134" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="2:7">
       <c r="B135" s="19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C135" s="19">
         <v>1</v>
       </c>
       <c r="D135" s="19"/>
       <c r="E135" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F135" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="2:7">
       <c r="B136" s="19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C136" s="19">
         <v>2</v>
       </c>
       <c r="D136" s="19"/>
       <c r="E136" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F136" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G136" s="19"/>
     </row>
     <row r="137" spans="2:7">
       <c r="B137" s="14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C137" s="14">
         <v>3</v>
       </c>
       <c r="D137" s="14"/>
       <c r="E137" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F137" s="14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G137" s="14"/>
     </row>
     <row r="138" spans="2:7">
       <c r="B138" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C138" s="14">
         <v>6</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F138" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="2:7">
       <c r="B139" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C139" s="14">
         <v>6</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F139" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G139" s="14"/>
     </row>
     <row r="140" spans="2:7">
       <c r="B140" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C140" s="15">
         <v>7</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G140" s="13"/>
     </row>
